--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486484_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486484_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5066</v>
+        <v>7.6183</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1448</v>
+        <v>6.2566</v>
       </c>
       <c r="F2" t="n">
         <v>1.3618</v>
@@ -610,10 +610,10 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0565</v>
+        <v>0.1682</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2776</v>
+        <v>0.3894</v>
       </c>
       <c r="U2" t="n">
         <v>-0.2211</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4855</v>
+        <v>4.8662</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0876</v>
+        <v>3.7149</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3979</v>
+        <v>1.1513</v>
       </c>
       <c r="G3" t="n">
         <v>4.436</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.603</v>
+        <v>-0.2223</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.0577</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0819</v>
+        <v>-0.1646</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0996</v>
+        <v>3.9901</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2247</v>
+        <v>1.9929</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1251</v>
+        <v>1.9971</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7569</v>
+        <v>1.3562</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1497</v>
+        <v>0.1219</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3928</v>
+        <v>1.2343</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0449</v>
+        <v>1.3149</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0698</v>
+        <v>0.7212</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1147</v>
+        <v>0.5937</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8018</v>
+        <v>0.0413</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0799</v>
+        <v>-0.5994</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2781</v>
+        <v>0.6407</v>
       </c>
       <c r="P4" t="n">
-        <v>0.87</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0962</v>
+        <v>1.6785</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1596</v>
+        <v>1.3327</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9366</v>
+        <v>0.3458</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8902</v>
+        <v>0.9554</v>
       </c>
       <c r="W4" t="n">
-        <v>3.0202</v>
+        <v>1.5204</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>M. BRAZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0912</v>
+        <v>3.38</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3715</v>
+        <v>3.8454</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7197</v>
+        <v>-0.4655</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3562</v>
+        <v>1.9429</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1219</v>
+        <v>0.7086</v>
       </c>
       <c r="I5" t="n">
         <v>1.2343</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3149</v>
+        <v>2.5797</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7212</v>
+        <v>1.241</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5937</v>
+        <v>1.3387</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0413</v>
+        <v>-0.6368</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5994</v>
+        <v>-0.5324</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6407</v>
+        <v>-0.1044</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7796</v>
+        <v>-0.4329</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7112</v>
+        <v>0.1358</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0684</v>
+        <v>-0.5687</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9554</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5204</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>-0.5649999999999999</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BRAZ</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5611</v>
+        <v>3.0044</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1807</v>
+        <v>3.6227</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6196</v>
+        <v>-0.6183</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9429</v>
+        <v>-0.7569</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7086</v>
+        <v>-1.1497</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2343</v>
+        <v>0.3928</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5797</v>
+        <v>0.0449</v>
       </c>
       <c r="K6" t="n">
-        <v>1.241</v>
+        <v>-0.0698</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3387</v>
+        <v>0.1147</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6368</v>
+        <v>-0.8018</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5324</v>
+        <v>-1.0799</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1044</v>
+        <v>0.2781</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2518</v>
+        <v>1.001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4711</v>
+        <v>0.5576</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7228</v>
+        <v>0.4434</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.8902</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>3.0202</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9329</v>
+        <v>2.4495</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5756</v>
+        <v>1.4939</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5086</v>
+        <v>0.9557</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2767</v>
+        <v>3.2998</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.597</v>
+        <v>1.989</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3203</v>
+        <v>1.3108</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.8009</v>
+        <v>3.94</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.9921</v>
+        <v>3.2698</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1912</v>
+        <v>0.6702</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5242</v>
+        <v>-0.6401</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3951</v>
+        <v>-1.2808</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1291</v>
+        <v>0.6407</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4478</v>
+        <v>-0.3049</v>
       </c>
       <c r="T7" t="n">
-        <v>3.0523</v>
+        <v>0.2091</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3955</v>
+        <v>-0.514</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5443</v>
+        <v>2.0647</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7395</v>
+        <v>1.695</v>
       </c>
       <c r="X7" t="n">
-        <v>1.2838</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.463</v>
+        <v>2.1513</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5998</v>
+        <v>0.4529</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8632</v>
+        <v>1.6984</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2998</v>
+        <v>1.9799</v>
       </c>
       <c r="H8" t="n">
-        <v>1.989</v>
+        <v>2.0285</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3108</v>
+        <v>-0.0486</v>
       </c>
       <c r="J8" t="n">
-        <v>3.94</v>
+        <v>2.1721</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2698</v>
+        <v>1.8828</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6702</v>
+        <v>0.2893</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6401</v>
+        <v>-0.1922</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2808</v>
+        <v>0.1457</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6407</v>
+        <v>-0.3379</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.6101</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.3501</v>
+        <v>-3.2626</v>
       </c>
       <c r="R8" t="n">
         <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2915</v>
+        <v>0.7592</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.4134</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6065</v>
+        <v>0.3458</v>
       </c>
       <c r="V8" t="n">
-        <v>2.0647</v>
+        <v>0.9347</v>
       </c>
       <c r="W8" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7311</v>
+        <v>0.9573</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6899</v>
+        <v>0.6563</v>
       </c>
       <c r="F9" t="n">
-        <v>1.421</v>
+        <v>0.301</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9799</v>
+        <v>0.768</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0285</v>
+        <v>-0.7117</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0486</v>
+        <v>1.4798</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1721</v>
+        <v>1.6232</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8828</v>
+        <v>-0.1944</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2893</v>
+        <v>1.8177</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1922</v>
+        <v>-0.8552</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1457</v>
+        <v>-0.5173</v>
       </c>
       <c r="O9" t="n">
         <v>-0.3379</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5225</v>
+        <v>-0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6611</v>
+        <v>0.6243</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7294</v>
+        <v>0.0781</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0684</v>
+        <v>0.5462</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2114</v>
+        <v>0.1324</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1513</v>
+        <v>-3.407</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3627</v>
+        <v>3.5394</v>
       </c>
       <c r="G10" t="n">
-        <v>0.768</v>
+        <v>-2.2767</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7117</v>
+        <v>-2.597</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4798</v>
+        <v>0.3203</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6232</v>
+        <v>-2.8009</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1944</v>
+        <v>-2.9921</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8177</v>
+        <v>0.1912</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8552</v>
+        <v>0.5242</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5173</v>
+        <v>0.3951</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3379</v>
+        <v>0.1291</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1216</v>
+        <v>1.6472</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7294</v>
+        <v>1.2209</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6078</v>
+        <v>0.4263</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>1.2838</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5733</v>
+        <v>-0.1764</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.2668</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5049</v>
+        <v>-0.4432</v>
       </c>
       <c r="G11" t="n">
         <v>0.596</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2569</v>
+        <v>0.14</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.2668</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1884</v>
+        <v>-0.1268</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8632</v>
+        <v>-1.1723</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9261</v>
+        <v>-2.0812</v>
       </c>
       <c r="F12" t="n">
-        <v>1.063</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-3.8321</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2962</v>
+        <v>-0.0129</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1971</v>
+        <v>0.0421</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09909999999999999</v>
+        <v>-0.055</v>
       </c>
       <c r="V12" t="n">
         <v>2.4552</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.911</v>
+        <v>-3.7809</v>
       </c>
       <c r="E13" t="n">
-        <v>0.076</v>
+        <v>0.1445</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.9871</v>
+        <v>-3.9254</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3758</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2021</v>
+        <v>0.3323</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0721</v>
+        <v>0.1406</v>
       </c>
       <c r="U13" t="n">
-        <v>0.13</v>
+        <v>0.1917</v>
       </c>
       <c r="V13" t="n">
         <v>-3.9549</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.7349</v>
+        <v>23.4199</v>
       </c>
       <c r="E14" t="n">
-        <v>16.27370000000001</v>
+        <v>16.9587</v>
       </c>
       <c r="F14" t="n">
-        <v>6.461200000000002</v>
+        <v>6.4611</v>
       </c>
       <c r="G14" t="n">
         <v>12.6298</v>
@@ -1546,13 +1546,13 @@
         <v>17.4006</v>
       </c>
       <c r="S14" t="n">
-        <v>4.692499999999999</v>
+        <v>5.3777</v>
       </c>
       <c r="T14" t="n">
-        <v>4.043699999999999</v>
+        <v>4.7288</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6488999999999999</v>
+        <v>0.649</v>
       </c>
       <c r="V14" t="n">
         <v>4.3246</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9208</v>
+        <v>5.3325</v>
       </c>
       <c r="E15" t="n">
-        <v>7.8801</v>
+        <v>7.2096</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9593</v>
+        <v>-1.8771</v>
       </c>
       <c r="G15" t="n">
         <v>3.1489</v>
@@ -1624,13 +1624,13 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3597</v>
+        <v>-0.2286</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5997</v>
+        <v>-0.0709</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.24</v>
+        <v>-0.1577</v>
       </c>
       <c r="V15" t="n">
         <v>2.6297</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0084</v>
+        <v>3.0406</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2159</v>
+        <v>4.1041</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2075</v>
+        <v>-1.0636</v>
       </c>
       <c r="G16" t="n">
         <v>3.3951</v>
@@ -1702,13 +1702,13 @@
         <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1268</v>
+        <v>-0.0946</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0769</v>
+        <v>-0.1887</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0499</v>
+        <v>0.094</v>
       </c>
       <c r="V16" t="n">
         <v>-1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1162</v>
+        <v>-1.5472</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.065</v>
+        <v>0.0467</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0512</v>
+        <v>-1.5939</v>
       </c>
       <c r="G17" t="n">
         <v>0.0963</v>
@@ -1780,13 +1780,13 @@
         <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2125</v>
+        <v>-0.6435</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1899</v>
+        <v>-0.0781</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0227</v>
+        <v>-0.5654</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5649999999999999</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4536</v>
+        <v>-2.4381</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2094</v>
+        <v>-2.7623</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7557</v>
+        <v>0.3242</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7566000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5893</v>
+        <v>-0.5738</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8904</v>
+        <v>-0.4434</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3011</v>
+        <v>-0.1304</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3252</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. NUGU</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0574</v>
+        <v>-3.3259</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4463</v>
+        <v>-2.0567</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6111</v>
+        <v>-1.2692</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.3474</v>
+        <v>-1.4501</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3229</v>
+        <v>0.8209</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.6703</v>
+        <v>-2.271</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.3902</v>
+        <v>1.0331</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4752</v>
+        <v>1.2227</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.8655</v>
+        <v>-0.1896</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-2.4832</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1523</v>
+        <v>-0.4018</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-2.0814</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7401</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-4.3501</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2449</v>
+        <v>-0.3305</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5312</v>
+        <v>-0.0649</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2863</v>
+        <v>-0.2656</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.695</v>
+        <v>1.4997</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3698</v>
+        <v>1.3252</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1407</v>
+        <v>-3.4713</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2657</v>
+        <v>-0.5049</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8749</v>
+        <v>-2.9663</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.163</v>
+        <v>-2.9384</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.904</v>
+        <v>0.3191</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2591</v>
+        <v>-3.2575</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7468</v>
+        <v>0.4923</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2711</v>
+        <v>0.6054</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4757</v>
+        <v>-0.1131</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4162</v>
+        <v>-3.4307</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6328</v>
+        <v>-0.2863</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7834</v>
+        <v>-3.1444</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1952</v>
+        <v>-0.6204</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4386</v>
+        <v>-0.4747</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6338</v>
+        <v>-0.1457</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X20" t="n">
         <v>-1.13</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>M. NUGU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2587</v>
+        <v>-3.6778</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8401999999999999</v>
+        <v>-3.0051</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4184</v>
+        <v>-0.6727</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9384</v>
+        <v>-3.3474</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3191</v>
+        <v>0.3229</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.2575</v>
+        <v>-3.6703</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4923</v>
+        <v>-2.3902</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6054</v>
+        <v>0.4752</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1131</v>
+        <v>-2.8655</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4307</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2863</v>
+        <v>-0.1523</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.1444</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4078</v>
+        <v>-0.3755</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8099</v>
+        <v>-0.0276</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5979</v>
+        <v>-0.3479</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.695</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.3698</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3176</v>
+        <v>-3.8067</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5038</v>
+        <v>-1.2657</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8138</v>
+        <v>-2.541</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4501</v>
+        <v>-4.163</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8209</v>
+        <v>-1.904</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.271</v>
+        <v>-2.2591</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0331</v>
+        <v>-1.7468</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2227</v>
+        <v>-1.2711</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1896</v>
+        <v>-0.4757</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4832</v>
+        <v>-2.4162</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4018</v>
+        <v>-0.6328</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0814</v>
+        <v>-1.7834</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.0451</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3221</v>
+        <v>0.1388</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5119</v>
+        <v>0.4386</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8102</v>
+        <v>-0.2998</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4997</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1745</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0464</v>
+        <v>-4.954</v>
       </c>
       <c r="E23" t="n">
         <v>-4.6906</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3559</v>
+        <v>-0.2634</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2039</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2123</v>
+        <v>-0.1199</v>
       </c>
       <c r="T23" t="n">
         <v>0.1646</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.377</v>
+        <v>-0.2845</v>
       </c>
       <c r="V23" t="n">
         <v>0.3698</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2735</v>
+        <v>-6.3968</v>
       </c>
       <c r="E24" t="n">
         <v>-3.5361</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7375</v>
+        <v>-2.8608</v>
       </c>
       <c r="G24" t="n">
         <v>-1.411</v>
@@ -2326,13 +2326,13 @@
         <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2312</v>
+        <v>-0.3545</v>
       </c>
       <c r="T24" t="n">
         <v>0.0961</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3274</v>
+        <v>-0.4506</v>
       </c>
       <c r="V24" t="n">
         <v>-3.5438</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-22.7349</v>
+        <v>-21.2447</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.461099999999998</v>
+        <v>-6.461</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.2739</v>
+        <v>-14.7838</v>
       </c>
       <c r="G25" t="n">
         <v>-12.6301</v>
@@ -2404,13 +2404,13 @@
         <v>16.313</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.6926</v>
+        <v>-3.202499999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6488000000000002</v>
+        <v>-0.6490000000000002</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.0441</v>
+        <v>-2.5536</v>
       </c>
       <c r="V25" t="n">
         <v>-4.3248</v>
